--- a/data/nzd0436/nzd0436.xlsx
+++ b/data/nzd0436/nzd0436.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L673"/>
+  <dimension ref="A1:L674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28714,6 +28714,48 @@
       <c r="L673" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:26:27+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>362.69</v>
+      </c>
+      <c r="C674" t="n">
+        <v>353.43</v>
+      </c>
+      <c r="D674" t="n">
+        <v>351.62</v>
+      </c>
+      <c r="E674" t="n">
+        <v>355.19</v>
+      </c>
+      <c r="F674" t="n">
+        <v>353.63</v>
+      </c>
+      <c r="G674" t="n">
+        <v>354.76</v>
+      </c>
+      <c r="H674" t="n">
+        <v>353.94</v>
+      </c>
+      <c r="I674" t="n">
+        <v>344.6</v>
+      </c>
+      <c r="J674" t="n">
+        <v>336.05</v>
+      </c>
+      <c r="K674" t="n">
+        <v>336.05</v>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -28728,7 +28770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B707"/>
+  <dimension ref="A1:B709"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35801,6 +35843,26 @@
       </c>
       <c r="B707" t="n">
         <v>0.92</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -35969,28 +36031,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5760610102779521</v>
+        <v>-0.5742750301483706</v>
       </c>
       <c r="J2" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K2" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2689643451920957</v>
+        <v>0.2681360297422118</v>
       </c>
       <c r="M2" t="n">
-        <v>5.663951102062471</v>
+        <v>5.663699352186204</v>
       </c>
       <c r="N2" t="n">
-        <v>50.93309932929104</v>
+        <v>50.91504561307507</v>
       </c>
       <c r="O2" t="n">
-        <v>7.136742907607856</v>
+        <v>7.135477952672482</v>
       </c>
       <c r="P2" t="n">
-        <v>371.590799518682</v>
+        <v>371.5725902728598</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36047,28 +36109,28 @@
         <v>0.1156</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5523598964311385</v>
+        <v>-0.5492761056352978</v>
       </c>
       <c r="J3" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K3" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2123826870018468</v>
+        <v>0.2105882715312483</v>
       </c>
       <c r="M3" t="n">
-        <v>6.483764384444046</v>
+        <v>6.491533965169372</v>
       </c>
       <c r="N3" t="n">
-        <v>63.89394678509453</v>
+        <v>63.97081536816115</v>
       </c>
       <c r="O3" t="n">
-        <v>7.993368925871903</v>
+        <v>7.998175752517643</v>
       </c>
       <c r="P3" t="n">
-        <v>357.1679712439275</v>
+        <v>357.1365299620588</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36125,28 +36187,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4217601430768497</v>
+        <v>-0.4188414940006598</v>
       </c>
       <c r="J4" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K4" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1475036464718809</v>
+        <v>0.1458248673383891</v>
       </c>
       <c r="M4" t="n">
-        <v>6.009563348549506</v>
+        <v>6.01397308545811</v>
       </c>
       <c r="N4" t="n">
-        <v>58.05506809979902</v>
+        <v>58.12270416557868</v>
       </c>
       <c r="O4" t="n">
-        <v>7.619387645985668</v>
+        <v>7.623824772748826</v>
       </c>
       <c r="P4" t="n">
-        <v>352.506424937284</v>
+        <v>352.4766673842087</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36203,28 +36265,28 @@
         <v>0.0997</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3402673033007316</v>
+        <v>-0.3368719844877542</v>
       </c>
       <c r="J5" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K5" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08992472261167606</v>
+        <v>0.08829501637739279</v>
       </c>
       <c r="M5" t="n">
-        <v>6.371018096046604</v>
+        <v>6.376121992422134</v>
       </c>
       <c r="N5" t="n">
-        <v>66.16951357299905</v>
+        <v>66.27946666071986</v>
       </c>
       <c r="O5" t="n">
-        <v>8.134464553552315</v>
+        <v>8.141220219397081</v>
       </c>
       <c r="P5" t="n">
-        <v>352.2699640871449</v>
+        <v>352.2353465715933</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36281,28 +36343,28 @@
         <v>0.1118</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3204445796892885</v>
+        <v>-0.3176114708008765</v>
       </c>
       <c r="J6" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K6" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06539061244411148</v>
+        <v>0.06439630179807965</v>
       </c>
       <c r="M6" t="n">
-        <v>7.452323342890295</v>
+        <v>7.45383268244539</v>
       </c>
       <c r="N6" t="n">
-        <v>82.87811933288893</v>
+        <v>82.89998241783731</v>
       </c>
       <c r="O6" t="n">
-        <v>9.103742051095743</v>
+        <v>9.104942746543621</v>
       </c>
       <c r="P6" t="n">
-        <v>352.1474557947609</v>
+        <v>352.1185703803399</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36359,28 +36421,28 @@
         <v>0.1316</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3237418595718677</v>
+        <v>-0.3215682035651684</v>
       </c>
       <c r="J7" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K7" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07151184783041731</v>
+        <v>0.07075468583244282</v>
       </c>
       <c r="M7" t="n">
-        <v>7.073895270963518</v>
+        <v>7.073753126730413</v>
       </c>
       <c r="N7" t="n">
-        <v>76.84495735431879</v>
+        <v>76.81613460218598</v>
       </c>
       <c r="O7" t="n">
-        <v>8.766125561176887</v>
+        <v>8.764481422319633</v>
       </c>
       <c r="P7" t="n">
-        <v>355.6735950215296</v>
+        <v>355.6514331643491</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36437,28 +36499,28 @@
         <v>0.1775</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3117030097755557</v>
+        <v>-0.3104719981065683</v>
       </c>
       <c r="J8" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K8" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06873847937129074</v>
+        <v>0.06840908715697791</v>
       </c>
       <c r="M8" t="n">
-        <v>6.905665731772729</v>
+        <v>6.901719871421894</v>
       </c>
       <c r="N8" t="n">
-        <v>74.33152163909585</v>
+        <v>74.24845130601315</v>
       </c>
       <c r="O8" t="n">
-        <v>8.621573037392645</v>
+        <v>8.616754104998769</v>
       </c>
       <c r="P8" t="n">
-        <v>357.8340884061789</v>
+        <v>357.8215374299842</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36515,28 +36577,28 @@
         <v>0.1223</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3578779434825475</v>
+        <v>-0.3579031791005419</v>
       </c>
       <c r="J9" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K9" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09454645603947842</v>
+        <v>0.09482648821205841</v>
       </c>
       <c r="M9" t="n">
-        <v>6.917048681202098</v>
+        <v>6.906910250915859</v>
       </c>
       <c r="N9" t="n">
-        <v>69.26440027696852</v>
+        <v>69.1614929111939</v>
       </c>
       <c r="O9" t="n">
-        <v>8.322523672358555</v>
+        <v>8.316338912718379</v>
       </c>
       <c r="P9" t="n">
-        <v>354.0952205562279</v>
+        <v>354.095477850004</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36593,28 +36655,28 @@
         <v>0.111</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5082016392207883</v>
+        <v>-0.509889284126351</v>
       </c>
       <c r="J10" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K10" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2425458787223719</v>
+        <v>0.2441341009303933</v>
       </c>
       <c r="M10" t="n">
-        <v>5.392128916317728</v>
+        <v>5.393202404712505</v>
       </c>
       <c r="N10" t="n">
-        <v>45.54637842074841</v>
+        <v>45.53015761941694</v>
       </c>
       <c r="O10" t="n">
-        <v>6.748805703289169</v>
+        <v>6.747603842803528</v>
       </c>
       <c r="P10" t="n">
-        <v>355.3066548326205</v>
+        <v>355.3238614859517</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36671,28 +36733,28 @@
         <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5625490664842034</v>
+        <v>-0.5643211903237106</v>
       </c>
       <c r="J11" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="K11" t="n">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L11" t="n">
-        <v>0.346712482422612</v>
+        <v>0.3484654945400991</v>
       </c>
       <c r="M11" t="n">
-        <v>4.685481285139366</v>
+        <v>4.687380684474781</v>
       </c>
       <c r="N11" t="n">
-        <v>33.67247142795301</v>
+        <v>33.67917429065006</v>
       </c>
       <c r="O11" t="n">
-        <v>5.802798585850883</v>
+        <v>5.803376111424285</v>
       </c>
       <c r="P11" t="n">
-        <v>357.0276921563678</v>
+        <v>357.0457601281703</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36730,7 +36792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L673"/>
+  <dimension ref="A1:L674"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78459,6 +78521,68 @@
         </is>
       </c>
     </row>
+    <row r="674">
+      <c r="A674" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:26:27+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>-43.465887706988354,169.75880337697978</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>-43.46540021826767,169.75940612918862</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>-43.464873520177456,169.75993415989356</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>-43.46431456731631,169.76039776637177</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>-43.46377540211918,169.76090035141672</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>-43.46322350192532,169.7613745027552</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>-43.46267378552457,169.76182639214647</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>-43.462097541225056,169.7622351182157</t>
+        </is>
+      </c>
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>-43.46150650825129,169.76262563780713</t>
+        </is>
+      </c>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>-43.4608828787044,169.7628933262129</t>
+        </is>
+      </c>
+      <c r="L674" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0436/nzd0436.xlsx
+++ b/data/nzd0436/nzd0436.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L674"/>
+  <dimension ref="A1:L675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28756,6 +28756,48 @@
       <c r="L674" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:26:31+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>362.42</v>
+      </c>
+      <c r="C675" t="n">
+        <v>353.4</v>
+      </c>
+      <c r="D675" t="n">
+        <v>350.93</v>
+      </c>
+      <c r="E675" t="n">
+        <v>355.01</v>
+      </c>
+      <c r="F675" t="n">
+        <v>353.28</v>
+      </c>
+      <c r="G675" t="n">
+        <v>354.56</v>
+      </c>
+      <c r="H675" t="n">
+        <v>353.69</v>
+      </c>
+      <c r="I675" t="n">
+        <v>344.79</v>
+      </c>
+      <c r="J675" t="n">
+        <v>336.86</v>
+      </c>
+      <c r="K675" t="n">
+        <v>336.83</v>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -28770,7 +28812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B709"/>
+  <dimension ref="A1:B710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35863,6 +35905,16 @@
       </c>
       <c r="B709" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>1.06</v>
       </c>
     </row>
   </sheetData>
@@ -36031,28 +36083,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5742750301483706</v>
+        <v>-0.5725763483974197</v>
       </c>
       <c r="J2" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K2" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2681360297422118</v>
+        <v>0.2673843324401534</v>
       </c>
       <c r="M2" t="n">
-        <v>5.663699352186204</v>
+        <v>5.663031593841543</v>
       </c>
       <c r="N2" t="n">
-        <v>50.91504561307507</v>
+        <v>50.89182906457063</v>
       </c>
       <c r="O2" t="n">
-        <v>7.135477952672482</v>
+        <v>7.133850928115237</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5725902728598</v>
+        <v>371.5552533877032</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36109,28 +36161,28 @@
         <v>0.1156</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5492761056352978</v>
+        <v>-0.5462206922134113</v>
       </c>
       <c r="J3" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K3" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2105882715312483</v>
+        <v>0.2088177117578027</v>
       </c>
       <c r="M3" t="n">
-        <v>6.491533965169372</v>
+        <v>6.499159197619226</v>
       </c>
       <c r="N3" t="n">
-        <v>63.97081536816115</v>
+        <v>64.04519098463605</v>
       </c>
       <c r="O3" t="n">
-        <v>7.998175752517643</v>
+        <v>8.002823938125594</v>
       </c>
       <c r="P3" t="n">
-        <v>357.1365299620588</v>
+        <v>357.105346162285</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36187,28 +36239,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4188414940006598</v>
+        <v>-0.4161398941215769</v>
       </c>
       <c r="J4" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K4" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1458248673383891</v>
+        <v>0.1443240711994899</v>
       </c>
       <c r="M4" t="n">
-        <v>6.01397308545811</v>
+        <v>6.017377796303632</v>
       </c>
       <c r="N4" t="n">
-        <v>58.12270416557868</v>
+        <v>58.16881986410654</v>
       </c>
       <c r="O4" t="n">
-        <v>7.623824772748826</v>
+        <v>7.626848619456567</v>
       </c>
       <c r="P4" t="n">
-        <v>352.4766673842087</v>
+        <v>352.4490946344476</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36265,28 +36317,28 @@
         <v>0.0997</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3368719844877542</v>
+        <v>-0.3335518072930793</v>
       </c>
       <c r="J5" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K5" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08829501637739279</v>
+        <v>0.0867215156414658</v>
       </c>
       <c r="M5" t="n">
-        <v>6.376121992422134</v>
+        <v>6.38091010840662</v>
       </c>
       <c r="N5" t="n">
-        <v>66.27946666071986</v>
+        <v>66.38102707475693</v>
       </c>
       <c r="O5" t="n">
-        <v>8.141220219397081</v>
+        <v>8.14745525147312</v>
       </c>
       <c r="P5" t="n">
-        <v>352.2353465715933</v>
+        <v>352.2014605710571</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36343,28 +36395,28 @@
         <v>0.1118</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3176114708008765</v>
+        <v>-0.314894986026506</v>
       </c>
       <c r="J6" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K6" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06439630179807965</v>
+        <v>0.06345831108491529</v>
       </c>
       <c r="M6" t="n">
-        <v>7.45383268244539</v>
+        <v>7.454792543923135</v>
       </c>
       <c r="N6" t="n">
-        <v>82.89998241783731</v>
+        <v>82.91079901331788</v>
       </c>
       <c r="O6" t="n">
-        <v>9.104942746543621</v>
+        <v>9.105536722967948</v>
       </c>
       <c r="P6" t="n">
-        <v>352.1185703803399</v>
+        <v>352.0908457141178</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36421,28 +36473,28 @@
         <v>0.1316</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3215682035651684</v>
+        <v>-0.3194647875927651</v>
       </c>
       <c r="J7" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K7" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07075468583244282</v>
+        <v>0.07003152361041076</v>
       </c>
       <c r="M7" t="n">
-        <v>7.073753126730413</v>
+        <v>7.073254397618922</v>
       </c>
       <c r="N7" t="n">
-        <v>76.81613460218598</v>
+        <v>76.7823939381823</v>
       </c>
       <c r="O7" t="n">
-        <v>8.764481422319633</v>
+        <v>8.762556358630871</v>
       </c>
       <c r="P7" t="n">
-        <v>355.6514331643491</v>
+        <v>355.6299655285605</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36499,28 +36551,28 @@
         <v>0.1775</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3104719981065683</v>
+        <v>-0.309321368629487</v>
       </c>
       <c r="J8" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K8" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06840908715697791</v>
+        <v>0.06811459514156581</v>
       </c>
       <c r="M8" t="n">
-        <v>6.901719871421894</v>
+        <v>6.897362010101896</v>
       </c>
       <c r="N8" t="n">
-        <v>74.24845130601315</v>
+        <v>74.16229843882637</v>
       </c>
       <c r="O8" t="n">
-        <v>8.616754104998769</v>
+        <v>8.61175350546138</v>
       </c>
       <c r="P8" t="n">
-        <v>357.8215374299842</v>
+        <v>357.8097940112474</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36577,28 +36629,28 @@
         <v>0.1223</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3579031791005419</v>
+        <v>-0.3578722772641608</v>
       </c>
       <c r="J9" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K9" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09482648821205841</v>
+        <v>0.09507970206670646</v>
       </c>
       <c r="M9" t="n">
-        <v>6.906910250915859</v>
+        <v>6.896812205497895</v>
       </c>
       <c r="N9" t="n">
-        <v>69.1614929111939</v>
+        <v>69.05889673649531</v>
       </c>
       <c r="O9" t="n">
-        <v>8.316338912718379</v>
+        <v>8.310168273656997</v>
       </c>
       <c r="P9" t="n">
-        <v>354.095477850004</v>
+        <v>354.0951624633295</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36655,28 +36707,28 @@
         <v>0.111</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.509889284126351</v>
+        <v>-0.5113301670492565</v>
       </c>
       <c r="J10" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K10" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2441341009303933</v>
+        <v>0.2456014233123627</v>
       </c>
       <c r="M10" t="n">
-        <v>5.393202404712505</v>
+        <v>5.392958556361409</v>
       </c>
       <c r="N10" t="n">
-        <v>45.53015761941694</v>
+        <v>45.50025355989303</v>
       </c>
       <c r="O10" t="n">
-        <v>6.747603842803528</v>
+        <v>6.74538757669958</v>
       </c>
       <c r="P10" t="n">
-        <v>355.3238614859517</v>
+        <v>355.3385672551427</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36733,28 +36785,28 @@
         <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5643211903237106</v>
+        <v>-0.565855708991046</v>
       </c>
       <c r="J11" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="K11" t="n">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3484654945400991</v>
+        <v>0.3501205069810724</v>
       </c>
       <c r="M11" t="n">
-        <v>4.687380684474781</v>
+        <v>4.688097927145611</v>
       </c>
       <c r="N11" t="n">
-        <v>33.67917429065006</v>
+        <v>33.67190540443872</v>
       </c>
       <c r="O11" t="n">
-        <v>5.803376111424285</v>
+        <v>5.802749814048399</v>
       </c>
       <c r="P11" t="n">
-        <v>357.0457601281703</v>
+        <v>357.0614215514424</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36792,7 +36844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L674"/>
+  <dimension ref="A1:L675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78583,6 +78635,68 @@
         </is>
       </c>
     </row>
+    <row r="675">
+      <c r="A675" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-05 22:26:31+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>-43.46588913781184,169.75880607207395</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>-43.465400377246915,169.75940642864242</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>-43.46487714409445,169.7599410796812</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>-43.46431549238021,169.76039959123918</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>-43.46377717783758,169.7609039215246</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>-43.463224482468114,169.7613765740394</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>-43.462674790846684,169.76182915438022</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>-43.46209693123058,169.76223292597595</t>
+        </is>
+      </c>
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>-43.46150406401992,169.7626162128766</t>
+        </is>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>-43.46088061797308,169.7628842060098</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0436/nzd0436.xlsx
+++ b/data/nzd0436/nzd0436.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L675"/>
+  <dimension ref="A1:L676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28796,6 +28796,48 @@
         <v>336.83</v>
       </c>
       <c r="L675" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>357.85</v>
+      </c>
+      <c r="C676" t="n">
+        <v>348.65</v>
+      </c>
+      <c r="D676" t="n">
+        <v>344.21</v>
+      </c>
+      <c r="E676" t="n">
+        <v>350.22</v>
+      </c>
+      <c r="F676" t="n">
+        <v>349.65</v>
+      </c>
+      <c r="G676" t="n">
+        <v>351.47</v>
+      </c>
+      <c r="H676" t="n">
+        <v>351.13</v>
+      </c>
+      <c r="I676" t="n">
+        <v>345.65</v>
+      </c>
+      <c r="J676" t="n">
+        <v>339.46</v>
+      </c>
+      <c r="K676" t="n">
+        <v>342.18</v>
+      </c>
+      <c r="L676" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28812,7 +28854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B710"/>
+  <dimension ref="A1:B711"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35915,6 +35957,16 @@
       </c>
       <c r="B710" t="n">
         <v>1.06</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>1.15</v>
       </c>
     </row>
   </sheetData>
@@ -36083,28 +36135,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5725763483974197</v>
+        <v>-0.5721605021099526</v>
       </c>
       <c r="J2" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K2" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2673843324401534</v>
+        <v>0.2677128356570867</v>
       </c>
       <c r="M2" t="n">
-        <v>5.663031593841543</v>
+        <v>5.656501295635812</v>
       </c>
       <c r="N2" t="n">
-        <v>50.89182906457063</v>
+        <v>50.81950551274975</v>
       </c>
       <c r="O2" t="n">
-        <v>7.133850928115237</v>
+        <v>7.128780085873722</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5552533877032</v>
+        <v>371.5509787034522</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36161,28 +36213,28 @@
         <v>0.1156</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5462206922134113</v>
+        <v>-0.5444922941343088</v>
       </c>
       <c r="J3" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K3" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2088177117578027</v>
+        <v>0.2081612230023718</v>
       </c>
       <c r="M3" t="n">
-        <v>6.499159197619226</v>
+        <v>6.499202196653393</v>
       </c>
       <c r="N3" t="n">
-        <v>64.04519098463605</v>
+        <v>64.00337417884126</v>
       </c>
       <c r="O3" t="n">
-        <v>8.002823938125594</v>
+        <v>8.00021088339809</v>
       </c>
       <c r="P3" t="n">
-        <v>357.105346162285</v>
+        <v>357.0875791260731</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36239,28 +36291,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4161398941215769</v>
+        <v>-0.4153428447222296</v>
       </c>
       <c r="J4" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K4" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1443240711994899</v>
+        <v>0.1442205174500357</v>
       </c>
       <c r="M4" t="n">
-        <v>6.017377796303632</v>
+        <v>6.012039623091874</v>
       </c>
       <c r="N4" t="n">
-        <v>58.16881986410654</v>
+        <v>58.09392855389823</v>
       </c>
       <c r="O4" t="n">
-        <v>7.626848619456567</v>
+        <v>7.621937322879153</v>
       </c>
       <c r="P4" t="n">
-        <v>352.4490946344476</v>
+        <v>352.440901379831</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36317,28 +36369,28 @@
         <v>0.0997</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3335518072930793</v>
+        <v>-0.3315788049321411</v>
       </c>
       <c r="J5" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K5" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0867215156414658</v>
+        <v>0.08595490894031355</v>
       </c>
       <c r="M5" t="n">
-        <v>6.38091010840662</v>
+        <v>6.379854166984167</v>
       </c>
       <c r="N5" t="n">
-        <v>66.38102707475693</v>
+        <v>66.35183215430459</v>
       </c>
       <c r="O5" t="n">
-        <v>8.14745525147312</v>
+        <v>8.145663395593056</v>
       </c>
       <c r="P5" t="n">
-        <v>352.2014605710571</v>
+        <v>352.1811791296362</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36395,28 +36447,28 @@
         <v>0.1118</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.314894986026506</v>
+        <v>-0.3131965672832097</v>
       </c>
       <c r="J6" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K6" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06345831108491529</v>
+        <v>0.06297004198296774</v>
       </c>
       <c r="M6" t="n">
-        <v>7.454792543923135</v>
+        <v>7.451129586394346</v>
       </c>
       <c r="N6" t="n">
-        <v>82.91079901331788</v>
+        <v>82.83920828335876</v>
       </c>
       <c r="O6" t="n">
-        <v>9.105536722967948</v>
+        <v>9.101604709245439</v>
       </c>
       <c r="P6" t="n">
-        <v>352.0908457141178</v>
+        <v>352.0733868499359</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36473,28 +36525,28 @@
         <v>0.1316</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3194647875927651</v>
+        <v>-0.3182277092368272</v>
       </c>
       <c r="J7" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K7" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07003152361041076</v>
+        <v>0.06971149079646677</v>
       </c>
       <c r="M7" t="n">
-        <v>7.073254397618922</v>
+        <v>7.068553170150373</v>
       </c>
       <c r="N7" t="n">
-        <v>76.7823939381823</v>
+        <v>76.69582632705179</v>
       </c>
       <c r="O7" t="n">
-        <v>8.762556358630871</v>
+        <v>8.757615333357123</v>
       </c>
       <c r="P7" t="n">
-        <v>355.6299655285605</v>
+        <v>355.6172490043913</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36551,28 +36603,28 @@
         <v>0.1775</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.309321368629487</v>
+        <v>-0.3088882052367515</v>
       </c>
       <c r="J8" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K8" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06811459514156581</v>
+        <v>0.06813631569536627</v>
       </c>
       <c r="M8" t="n">
-        <v>6.897362010101896</v>
+        <v>6.889323117086764</v>
       </c>
       <c r="N8" t="n">
-        <v>74.16229843882637</v>
+        <v>74.05576127849974</v>
       </c>
       <c r="O8" t="n">
-        <v>8.61175350546138</v>
+        <v>8.605565715192682</v>
       </c>
       <c r="P8" t="n">
-        <v>357.8097940112474</v>
+        <v>357.8053413161319</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36629,28 +36681,28 @@
         <v>0.1223</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3578722772641608</v>
+        <v>-0.3575764836749477</v>
       </c>
       <c r="J9" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K9" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09507970206670646</v>
+        <v>0.09521000737765517</v>
       </c>
       <c r="M9" t="n">
-        <v>6.896812205497895</v>
+        <v>6.888003551048601</v>
       </c>
       <c r="N9" t="n">
-        <v>69.05889673649531</v>
+        <v>68.95814142724662</v>
       </c>
       <c r="O9" t="n">
-        <v>8.310168273656997</v>
+        <v>8.304103890682402</v>
       </c>
       <c r="P9" t="n">
-        <v>354.0951624633295</v>
+        <v>354.0921218585785</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36707,28 +36759,28 @@
         <v>0.111</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5113301670492565</v>
+        <v>-0.5120065263897758</v>
       </c>
       <c r="J10" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K10" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2456014233123627</v>
+        <v>0.2466506485666573</v>
       </c>
       <c r="M10" t="n">
-        <v>5.392958556361409</v>
+        <v>5.388555350852863</v>
       </c>
       <c r="N10" t="n">
-        <v>45.50025355989303</v>
+        <v>45.44097174776545</v>
       </c>
       <c r="O10" t="n">
-        <v>6.74538757669958</v>
+        <v>6.740991896432264</v>
       </c>
       <c r="P10" t="n">
-        <v>355.3385672551427</v>
+        <v>355.3455198785231</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36785,28 +36837,28 @@
         <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.565855708991046</v>
+        <v>-0.5658288208697098</v>
       </c>
       <c r="J11" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="K11" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3501205069810724</v>
+        <v>0.3508249263351872</v>
       </c>
       <c r="M11" t="n">
-        <v>4.688097927145611</v>
+        <v>4.681294891884488</v>
       </c>
       <c r="N11" t="n">
-        <v>33.67190540443872</v>
+        <v>33.62203394238818</v>
       </c>
       <c r="O11" t="n">
-        <v>5.802749814048399</v>
+        <v>5.798450995083789</v>
       </c>
       <c r="P11" t="n">
-        <v>357.0614215514424</v>
+        <v>357.0611451554945</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36844,7 +36896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L675"/>
+  <dimension ref="A1:L676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78697,6 +78749,68 @@
         </is>
       </c>
     </row>
+    <row r="676">
+      <c r="A676" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:14+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>-43.46591335581518,169.75885168905762</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>-43.46542554895062,169.75945384218033</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>-43.464912437874084,169.76000847243975</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>-43.46434010934858,169.7604481530093</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>-43.46379559456808,169.76094094865584</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>-43.463239631849646,169.7614085753889</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>-43.46268508534155,169.76185743965942</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>-43.462094170202455,169.76222300320717</t>
+        </is>
+      </c>
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>-43.4614962183339,169.76258596001855</t>
+        </is>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>-43.460865111655856,169.76282165078996</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0436/nzd0436.xlsx
+++ b/data/nzd0436/nzd0436.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L676"/>
+  <dimension ref="A1:L679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28838,6 +28838,132 @@
         <v>342.18</v>
       </c>
       <c r="L676" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="C677" t="n">
+        <v>349.09</v>
+      </c>
+      <c r="D677" t="n">
+        <v>343.95</v>
+      </c>
+      <c r="E677" t="n">
+        <v>350.63</v>
+      </c>
+      <c r="F677" t="n">
+        <v>348.84</v>
+      </c>
+      <c r="G677" t="n">
+        <v>351.16</v>
+      </c>
+      <c r="H677" t="n">
+        <v>351.04</v>
+      </c>
+      <c r="I677" t="n">
+        <v>346.37</v>
+      </c>
+      <c r="J677" t="n">
+        <v>343.4</v>
+      </c>
+      <c r="K677" t="n">
+        <v>346.18</v>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:07+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>355.75</v>
+      </c>
+      <c r="C678" t="n">
+        <v>347.95</v>
+      </c>
+      <c r="D678" t="n">
+        <v>344.14</v>
+      </c>
+      <c r="E678" t="n">
+        <v>350.33</v>
+      </c>
+      <c r="F678" t="n">
+        <v>349</v>
+      </c>
+      <c r="G678" t="n">
+        <v>351.26</v>
+      </c>
+      <c r="H678" t="n">
+        <v>350.38</v>
+      </c>
+      <c r="I678" t="n">
+        <v>344.85</v>
+      </c>
+      <c r="J678" t="n">
+        <v>342.4</v>
+      </c>
+      <c r="K678" t="n">
+        <v>345.88</v>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>355.46</v>
+      </c>
+      <c r="C679" t="n">
+        <v>348.08</v>
+      </c>
+      <c r="D679" t="n">
+        <v>344.42</v>
+      </c>
+      <c r="E679" t="n">
+        <v>350.43</v>
+      </c>
+      <c r="F679" t="n">
+        <v>349.32</v>
+      </c>
+      <c r="G679" t="n">
+        <v>351.73</v>
+      </c>
+      <c r="H679" t="n">
+        <v>351.35</v>
+      </c>
+      <c r="I679" t="n">
+        <v>346.3</v>
+      </c>
+      <c r="J679" t="n">
+        <v>343.89</v>
+      </c>
+      <c r="K679" t="n">
+        <v>347.23</v>
+      </c>
+      <c r="L679" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28854,7 +28980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B711"/>
+  <dimension ref="A1:B714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35967,6 +36093,36 @@
       </c>
       <c r="B711" t="n">
         <v>1.15</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -36135,28 +36291,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5721605021099526</v>
+        <v>-0.5722636927698604</v>
       </c>
       <c r="J2" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="K2" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2677128356570867</v>
+        <v>0.2696590067546345</v>
       </c>
       <c r="M2" t="n">
-        <v>5.656501295635812</v>
+        <v>5.635392842987661</v>
       </c>
       <c r="N2" t="n">
-        <v>50.81950551274975</v>
+        <v>50.59819375404125</v>
       </c>
       <c r="O2" t="n">
-        <v>7.128780085873722</v>
+        <v>7.113240734998447</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5509787034522</v>
+        <v>371.5520517884831</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36213,28 +36369,28 @@
         <v>0.1156</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5444922941343088</v>
+        <v>-0.539557726465092</v>
       </c>
       <c r="J3" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="K3" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2081612230023718</v>
+        <v>0.2063758832383428</v>
       </c>
       <c r="M3" t="n">
-        <v>6.499202196653393</v>
+        <v>6.497770575296468</v>
       </c>
       <c r="N3" t="n">
-        <v>64.00337417884126</v>
+        <v>63.86510408437792</v>
       </c>
       <c r="O3" t="n">
-        <v>8.00021088339809</v>
+        <v>7.991564557980992</v>
       </c>
       <c r="P3" t="n">
-        <v>357.0875791260731</v>
+        <v>357.0366435513303</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36291,28 +36447,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4153428447222296</v>
+        <v>-0.4129725152574847</v>
       </c>
       <c r="J4" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="K4" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1442205174500357</v>
+        <v>0.143923472838372</v>
       </c>
       <c r="M4" t="n">
-        <v>6.012039623091874</v>
+        <v>5.995999119601422</v>
       </c>
       <c r="N4" t="n">
-        <v>58.09392855389823</v>
+        <v>57.87022054810664</v>
       </c>
       <c r="O4" t="n">
-        <v>7.621937322879153</v>
+        <v>7.607247895796919</v>
       </c>
       <c r="P4" t="n">
-        <v>352.440901379831</v>
+        <v>352.4164305019332</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36369,28 +36525,28 @@
         <v>0.0997</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3315788049321411</v>
+        <v>-0.3254874924651715</v>
       </c>
       <c r="J5" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="K5" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08595490894031355</v>
+        <v>0.0835671398572515</v>
       </c>
       <c r="M5" t="n">
-        <v>6.379854166984167</v>
+        <v>6.377518942147399</v>
       </c>
       <c r="N5" t="n">
-        <v>66.35183215430459</v>
+        <v>66.27742154580515</v>
       </c>
       <c r="O5" t="n">
-        <v>8.145663395593056</v>
+        <v>8.141094615947241</v>
       </c>
       <c r="P5" t="n">
-        <v>352.1811791296362</v>
+        <v>352.1182996654466</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36447,28 +36603,28 @@
         <v>0.1118</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3131965672832097</v>
+        <v>-0.3086432933488563</v>
       </c>
       <c r="J6" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="K6" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06297004198296774</v>
+        <v>0.06173293680612513</v>
       </c>
       <c r="M6" t="n">
-        <v>7.451129586394346</v>
+        <v>7.43786692174369</v>
       </c>
       <c r="N6" t="n">
-        <v>82.83920828335876</v>
+        <v>82.5952557837216</v>
       </c>
       <c r="O6" t="n">
-        <v>9.101604709245439</v>
+        <v>9.088193207878097</v>
       </c>
       <c r="P6" t="n">
-        <v>352.0733868499359</v>
+        <v>352.0263815811143</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36525,28 +36681,28 @@
         <v>0.1316</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3182277092368272</v>
+        <v>-0.3146034680790852</v>
       </c>
       <c r="J7" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="K7" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06971149079646677</v>
+        <v>0.06878896260736167</v>
       </c>
       <c r="M7" t="n">
-        <v>7.068553170150373</v>
+        <v>7.053965214954689</v>
       </c>
       <c r="N7" t="n">
-        <v>76.69582632705179</v>
+        <v>76.43429198655643</v>
       </c>
       <c r="O7" t="n">
-        <v>8.757615333357123</v>
+        <v>8.742670758215503</v>
       </c>
       <c r="P7" t="n">
-        <v>355.6172490043913</v>
+        <v>355.5798335380572</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36603,28 +36759,28 @@
         <v>0.1775</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3088882052367515</v>
+        <v>-0.3077544083605628</v>
       </c>
       <c r="J8" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="K8" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06813631569536627</v>
+        <v>0.06827273047029569</v>
       </c>
       <c r="M8" t="n">
-        <v>6.889323117086764</v>
+        <v>6.864492023058889</v>
       </c>
       <c r="N8" t="n">
-        <v>74.05576127849974</v>
+        <v>73.73640841504367</v>
       </c>
       <c r="O8" t="n">
-        <v>8.605565715192682</v>
+        <v>8.586990649525809</v>
       </c>
       <c r="P8" t="n">
-        <v>357.8053413161319</v>
+        <v>357.7936348220652</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36681,28 +36837,28 @@
         <v>0.1223</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3575764836749477</v>
+        <v>-0.3565095003880567</v>
       </c>
       <c r="J9" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="K9" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09521000737765517</v>
+        <v>0.09551262178066522</v>
       </c>
       <c r="M9" t="n">
-        <v>6.888003551048601</v>
+        <v>6.862539048301276</v>
       </c>
       <c r="N9" t="n">
-        <v>68.95814142724662</v>
+        <v>68.66190364234468</v>
       </c>
       <c r="O9" t="n">
-        <v>8.304103890682402</v>
+        <v>8.286247862714745</v>
       </c>
       <c r="P9" t="n">
-        <v>354.0921218585785</v>
+        <v>354.0811058909295</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36759,28 +36915,28 @@
         <v>0.111</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5120065263897758</v>
+        <v>-0.5107327786950309</v>
       </c>
       <c r="J10" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="K10" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2466506485666573</v>
+        <v>0.2474658238081539</v>
       </c>
       <c r="M10" t="n">
-        <v>5.388555350852863</v>
+        <v>5.370970463103435</v>
       </c>
       <c r="N10" t="n">
-        <v>45.44097174776545</v>
+        <v>45.25122521567016</v>
       </c>
       <c r="O10" t="n">
-        <v>6.740991896432264</v>
+        <v>6.726903092483952</v>
       </c>
       <c r="P10" t="n">
-        <v>355.3455198785231</v>
+        <v>355.3323672841073</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36837,28 +36993,28 @@
         <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5658288208697098</v>
+        <v>-0.5620535740865477</v>
       </c>
       <c r="J11" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="K11" t="n">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3508249263351872</v>
+        <v>0.3493844155883782</v>
       </c>
       <c r="M11" t="n">
-        <v>4.681294891884488</v>
+        <v>4.680397864602222</v>
       </c>
       <c r="N11" t="n">
-        <v>33.62203394238818</v>
+        <v>33.55894047326542</v>
       </c>
       <c r="O11" t="n">
-        <v>5.798450995083789</v>
+        <v>5.793007895149584</v>
       </c>
       <c r="P11" t="n">
-        <v>357.0611451554945</v>
+        <v>357.0221678694411</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36896,7 +37052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L676"/>
+  <dimension ref="A1:L679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78811,6 +78967,192 @@
         </is>
       </c>
     </row>
+    <row r="677">
+      <c r="A677" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>-43.46591521058498,169.7588551827012</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>-43.465423217256756,169.7594494501878</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>-43.464913803406475,169.76001107989927</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>-43.46433800226019,169.76044399636353</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>-43.463799704084906,169.7609492109114</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>-43.463241151690035,169.76141178588117</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>-43.46268544725726,169.76185843406395</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>-43.46209185864339,169.7622146957736</t>
+        </is>
+      </c>
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>-43.46148432908717,169.76254011531867</t>
+        </is>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>-43.46085351812589,169.76277488055425</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:07+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>-43.46592448443241,169.75887265092246</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>-43.465429258463296,169.75946082944193</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>-43.46491280551743,169.76000917444807</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>-43.4643395440322,169.76044703781164</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>-43.46379889232854,169.76094757886082</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>-43.46324066141896,169.76141075023847</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>-43.46268810130555,169.7618657263642</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>-43.46209673860075,169.76223223368973</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>-43.461487346664164,169.76255175102753</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>-43.46085438764128,169.7627783883213</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>-43.46592602124116,169.7588755456568</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>-43.46542856955383,169.75945953180758</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>-43.46491133494405,169.76000636641487</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>-43.464339030108206,169.7604460239956</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>-43.46379726881574,169.76094431475983</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>-43.46323835714473,169.76140588271807</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>-43.46268420065866,169.76185500889287</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>-43.46209208337832,169.76221550344073</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>-43.46148285047402,169.76253441382178</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>-43.46085047482118,169.7627626033705</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0436/nzd0436.xlsx
+++ b/data/nzd0436/nzd0436.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L679"/>
+  <dimension ref="A1:L681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28964,6 +28964,90 @@
         <v>347.23</v>
       </c>
       <c r="L679" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:33+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>354.24</v>
+      </c>
+      <c r="C680" t="n">
+        <v>346.5</v>
+      </c>
+      <c r="D680" t="n">
+        <v>343.15</v>
+      </c>
+      <c r="E680" t="n">
+        <v>350.53</v>
+      </c>
+      <c r="F680" t="n">
+        <v>348.85</v>
+      </c>
+      <c r="G680" t="n">
+        <v>350.62</v>
+      </c>
+      <c r="H680" t="n">
+        <v>348.34</v>
+      </c>
+      <c r="I680" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="J680" t="n">
+        <v>343.45</v>
+      </c>
+      <c r="K680" t="n">
+        <v>347.38</v>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:19:45+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>355.98</v>
+      </c>
+      <c r="C681" t="n">
+        <v>348.5</v>
+      </c>
+      <c r="D681" t="n">
+        <v>345.92</v>
+      </c>
+      <c r="E681" t="n">
+        <v>352.09</v>
+      </c>
+      <c r="F681" t="n">
+        <v>350.66</v>
+      </c>
+      <c r="G681" t="n">
+        <v>352.65</v>
+      </c>
+      <c r="H681" t="n">
+        <v>350.18</v>
+      </c>
+      <c r="I681" t="n">
+        <v>346.99</v>
+      </c>
+      <c r="J681" t="n">
+        <v>345.37</v>
+      </c>
+      <c r="K681" t="n">
+        <v>348.17</v>
+      </c>
+      <c r="L681" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -28980,7 +29064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B714"/>
+  <dimension ref="A1:B716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36123,6 +36207,26 @@
       </c>
       <c r="B714" t="n">
         <v>0.65</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>0.49</v>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>-0.63</v>
       </c>
     </row>
   </sheetData>
@@ -36291,28 +36395,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5722636927698604</v>
+        <v>-0.5729397044267556</v>
       </c>
       <c r="J2" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K2" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2696590067546345</v>
+        <v>0.2713715446126778</v>
       </c>
       <c r="M2" t="n">
-        <v>5.635392842987661</v>
+        <v>5.622690773302724</v>
       </c>
       <c r="N2" t="n">
-        <v>50.59819375404125</v>
+        <v>50.45567680115089</v>
       </c>
       <c r="O2" t="n">
-        <v>7.113240734998447</v>
+        <v>7.103215947804973</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5520517884831</v>
+        <v>371.5590631260644</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36369,28 +36473,28 @@
         <v>0.1156</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.539557726465092</v>
+        <v>-0.536775413014063</v>
       </c>
       <c r="J3" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K3" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2063758832383428</v>
+        <v>0.2055548043245667</v>
       </c>
       <c r="M3" t="n">
-        <v>6.497770575296468</v>
+        <v>6.493971796735353</v>
       </c>
       <c r="N3" t="n">
-        <v>63.86510408437792</v>
+        <v>63.74878563773481</v>
       </c>
       <c r="O3" t="n">
-        <v>7.991564557980992</v>
+        <v>7.984283664658641</v>
       </c>
       <c r="P3" t="n">
-        <v>357.0366435513303</v>
+        <v>357.0077731635738</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36447,28 +36551,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4129725152574847</v>
+        <v>-0.4111740697733207</v>
       </c>
       <c r="J4" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K4" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L4" t="n">
-        <v>0.143923472838372</v>
+        <v>0.1435688209894016</v>
       </c>
       <c r="M4" t="n">
-        <v>5.995999119601422</v>
+        <v>5.986330554281042</v>
       </c>
       <c r="N4" t="n">
-        <v>57.87022054810664</v>
+        <v>57.73433241089223</v>
       </c>
       <c r="O4" t="n">
-        <v>7.607247895796919</v>
+        <v>7.598311155177329</v>
       </c>
       <c r="P4" t="n">
-        <v>352.4164305019332</v>
+        <v>352.397766980163</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36525,28 +36629,28 @@
         <v>0.0997</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3254874924651715</v>
+        <v>-0.3209729856265818</v>
       </c>
       <c r="J5" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K5" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0835671398572515</v>
+        <v>0.08172885227818505</v>
       </c>
       <c r="M5" t="n">
-        <v>6.377518942147399</v>
+        <v>6.377881123115862</v>
       </c>
       <c r="N5" t="n">
-        <v>66.27742154580515</v>
+        <v>66.26479795967556</v>
       </c>
       <c r="O5" t="n">
-        <v>8.141094615947241</v>
+        <v>8.140319278730752</v>
       </c>
       <c r="P5" t="n">
-        <v>352.1182996654466</v>
+        <v>352.0714577959058</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36603,28 +36707,28 @@
         <v>0.1118</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3086432933488563</v>
+        <v>-0.3052254154868813</v>
       </c>
       <c r="J6" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K6" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06173293680612513</v>
+        <v>0.06074905501945715</v>
       </c>
       <c r="M6" t="n">
-        <v>7.43786692174369</v>
+        <v>7.430654390370996</v>
       </c>
       <c r="N6" t="n">
-        <v>82.5952557837216</v>
+        <v>82.45820500806218</v>
       </c>
       <c r="O6" t="n">
-        <v>9.088193207878097</v>
+        <v>9.080650032242305</v>
       </c>
       <c r="P6" t="n">
-        <v>352.0263815811143</v>
+        <v>351.9909172679114</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36681,28 +36785,28 @@
         <v>0.1316</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3146034680790852</v>
+        <v>-0.3120544269181821</v>
       </c>
       <c r="J7" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K7" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06878896260736167</v>
+        <v>0.06811157290154501</v>
       </c>
       <c r="M7" t="n">
-        <v>7.053965214954689</v>
+        <v>7.044784844956118</v>
       </c>
       <c r="N7" t="n">
-        <v>76.43429198655643</v>
+        <v>76.27005863663845</v>
       </c>
       <c r="O7" t="n">
-        <v>8.742670758215503</v>
+        <v>8.733273076953363</v>
       </c>
       <c r="P7" t="n">
-        <v>355.5798335380572</v>
+        <v>355.5533834000174</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36759,28 +36863,28 @@
         <v>0.1775</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3077544083605628</v>
+        <v>-0.3079419640809525</v>
       </c>
       <c r="J8" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K8" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06827273047029569</v>
+        <v>0.06875920104304112</v>
       </c>
       <c r="M8" t="n">
-        <v>6.864492023058889</v>
+        <v>6.847034857052019</v>
       </c>
       <c r="N8" t="n">
-        <v>73.73640841504367</v>
+        <v>73.52233634638212</v>
       </c>
       <c r="O8" t="n">
-        <v>8.586990649525809</v>
+        <v>8.574516682961328</v>
       </c>
       <c r="P8" t="n">
-        <v>357.7936348220652</v>
+        <v>357.7955781259735</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36837,28 +36941,28 @@
         <v>0.1223</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3565095003880567</v>
+        <v>-0.3559233469070311</v>
       </c>
       <c r="J9" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K9" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09551262178066522</v>
+        <v>0.09577403361872505</v>
       </c>
       <c r="M9" t="n">
-        <v>6.862539048301276</v>
+        <v>6.84622893782949</v>
       </c>
       <c r="N9" t="n">
-        <v>68.66190364234468</v>
+        <v>68.46876975009215</v>
       </c>
       <c r="O9" t="n">
-        <v>8.286247862714745</v>
+        <v>8.274585775136551</v>
       </c>
       <c r="P9" t="n">
-        <v>354.0811058909295</v>
+        <v>354.0750202973514</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36915,28 +37019,28 @@
         <v>0.111</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5107327786950309</v>
+        <v>-0.5091832949666082</v>
       </c>
       <c r="J10" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K10" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2474658238081539</v>
+        <v>0.2474348035889355</v>
       </c>
       <c r="M10" t="n">
-        <v>5.370970463103435</v>
+        <v>5.36268567074591</v>
       </c>
       <c r="N10" t="n">
-        <v>45.25122521567016</v>
+        <v>45.14212645615261</v>
       </c>
       <c r="O10" t="n">
-        <v>6.726903092483952</v>
+        <v>6.718789061739668</v>
       </c>
       <c r="P10" t="n">
-        <v>355.3323672841073</v>
+        <v>355.3162880574699</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36993,28 +37097,28 @@
         <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5620535740865477</v>
+        <v>-0.5587590825212385</v>
       </c>
       <c r="J11" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="K11" t="n">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3493844155883782</v>
+        <v>0.3475230868987637</v>
       </c>
       <c r="M11" t="n">
-        <v>4.680397864602222</v>
+        <v>4.683776986012949</v>
       </c>
       <c r="N11" t="n">
-        <v>33.55894047326542</v>
+        <v>33.5568398131566</v>
       </c>
       <c r="O11" t="n">
-        <v>5.793007895149584</v>
+        <v>5.792826582347913</v>
       </c>
       <c r="P11" t="n">
-        <v>357.0221678694411</v>
+        <v>356.9879851968049</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37052,7 +37156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L679"/>
+  <dimension ref="A1:L681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79153,6 +79257,130 @@
         </is>
       </c>
     </row>
+    <row r="680">
+      <c r="A680" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:33+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>-43.46593248643588,169.7588877235063</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>-43.46543694245252,169.759475303058</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>-43.46491800504424,169.7600191028524</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>-43.464338516184185,169.76044501017955</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>-43.46379965335014,169.76094910890822</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>-43.46324379915375,169.76141737835198</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>-43.462696304724766,169.76188826620546</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>-43.46209882542382,169.76223973345742</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>-43.461484178208295,169.76253953353324</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>-43.46085004006327,169.76276084948725</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-21 22:19:45+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>-43.46592326558404,169.7588703550988</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>-43.46542634384623,169.7594553394506</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>-43.46490345687121,169.75999132338202</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>-43.46433049896867,169.7604291946517</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>-43.46379047035495,169.7609306463388</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>-43.463233846649935,169.7613963548069</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>-43.46268890556253,169.76186793615227</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>-43.462089868133724,169.76220754215075</t>
+        </is>
+      </c>
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>-43.46147838445712,169.76251719297582</t>
+        </is>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>-43.460847750337784,169.76275161236904</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0436/nzd0436.xlsx
+++ b/data/nzd0436/nzd0436.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L681"/>
+  <dimension ref="A1:L685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29048,6 +29048,174 @@
         <v>348.17</v>
       </c>
       <c r="L681" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:29+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="C682" t="n">
+        <v>347.81</v>
+      </c>
+      <c r="D682" t="n">
+        <v>345.91</v>
+      </c>
+      <c r="E682" t="n">
+        <v>351.95</v>
+      </c>
+      <c r="F682" t="n">
+        <v>350.94</v>
+      </c>
+      <c r="G682" t="n">
+        <v>352.41</v>
+      </c>
+      <c r="H682" t="n">
+        <v>350.14</v>
+      </c>
+      <c r="I682" t="n">
+        <v>347.77</v>
+      </c>
+      <c r="J682" t="n">
+        <v>345.77</v>
+      </c>
+      <c r="K682" t="n">
+        <v>347.95</v>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:25:37+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>357.6</v>
+      </c>
+      <c r="C683" t="n">
+        <v>348.92</v>
+      </c>
+      <c r="D683" t="n">
+        <v>347.16</v>
+      </c>
+      <c r="E683" t="n">
+        <v>352.98</v>
+      </c>
+      <c r="F683" t="n">
+        <v>351.78</v>
+      </c>
+      <c r="G683" t="n">
+        <v>353.79</v>
+      </c>
+      <c r="H683" t="n">
+        <v>351.42</v>
+      </c>
+      <c r="I683" t="n">
+        <v>349.83</v>
+      </c>
+      <c r="J683" t="n">
+        <v>347.8</v>
+      </c>
+      <c r="K683" t="n">
+        <v>348.56</v>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-22 22:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>356.77</v>
+      </c>
+      <c r="C684" t="n">
+        <v>348.75</v>
+      </c>
+      <c r="D684" t="n">
+        <v>350.46</v>
+      </c>
+      <c r="E684" t="n">
+        <v>354.1</v>
+      </c>
+      <c r="F684" t="n">
+        <v>352.33</v>
+      </c>
+      <c r="G684" t="n">
+        <v>354.33</v>
+      </c>
+      <c r="H684" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="I684" t="n">
+        <v>352.31</v>
+      </c>
+      <c r="J684" t="n">
+        <v>349.97</v>
+      </c>
+      <c r="K684" t="n">
+        <v>349.58</v>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:19:18+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>356.77</v>
+      </c>
+      <c r="C685" t="n">
+        <v>348.75</v>
+      </c>
+      <c r="D685" t="n">
+        <v>351.16</v>
+      </c>
+      <c r="E685" t="n">
+        <v>354.93</v>
+      </c>
+      <c r="F685" t="n">
+        <v>352.33</v>
+      </c>
+      <c r="G685" t="n">
+        <v>354.33</v>
+      </c>
+      <c r="H685" t="n">
+        <v>356.23</v>
+      </c>
+      <c r="I685" t="n">
+        <v>354.61</v>
+      </c>
+      <c r="J685" t="n">
+        <v>352.3</v>
+      </c>
+      <c r="K685" t="n">
+        <v>349.23</v>
+      </c>
+      <c r="L685" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29064,7 +29232,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B716"/>
+  <dimension ref="A1:B720"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36227,6 +36395,46 @@
       </c>
       <c r="B716" t="n">
         <v>-0.63</v>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B718" t="n">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>2026-05-22 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B719" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B720" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -36395,28 +36603,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5729397044267556</v>
+        <v>-0.5724045200626597</v>
       </c>
       <c r="J2" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K2" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2713715446126778</v>
+        <v>0.273526280119009</v>
       </c>
       <c r="M2" t="n">
-        <v>5.622690773302724</v>
+        <v>5.593870189135133</v>
       </c>
       <c r="N2" t="n">
-        <v>50.45567680115089</v>
+        <v>50.16463718059923</v>
       </c>
       <c r="O2" t="n">
-        <v>7.103215947804973</v>
+        <v>7.082699851087806</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5590631260644</v>
+        <v>371.5534860175762</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36473,28 +36681,28 @@
         <v>0.1156</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.536775413014063</v>
+        <v>-0.53008573159374</v>
       </c>
       <c r="J3" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K3" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2055548043245667</v>
+        <v>0.2030464988578015</v>
       </c>
       <c r="M3" t="n">
-        <v>6.493971796735353</v>
+        <v>6.492636965242941</v>
       </c>
       <c r="N3" t="n">
-        <v>63.74878563773481</v>
+        <v>63.57705747345776</v>
       </c>
       <c r="O3" t="n">
-        <v>7.984283664658641</v>
+        <v>7.973522275221771</v>
       </c>
       <c r="P3" t="n">
-        <v>357.0077731635738</v>
+        <v>356.9381301355536</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36551,28 +36759,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4111740697733207</v>
+        <v>-0.4029292295784565</v>
       </c>
       <c r="J4" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K4" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1435688209894016</v>
+        <v>0.1395040811515191</v>
       </c>
       <c r="M4" t="n">
-        <v>5.986330554281042</v>
+        <v>5.98794151875324</v>
       </c>
       <c r="N4" t="n">
-        <v>57.73433241089223</v>
+        <v>57.72848577988985</v>
       </c>
       <c r="O4" t="n">
-        <v>7.598311155177329</v>
+        <v>7.597926413166283</v>
       </c>
       <c r="P4" t="n">
-        <v>352.397766980163</v>
+        <v>352.311912442501</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36629,28 +36837,28 @@
         <v>0.0997</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3209729856265818</v>
+        <v>-0.3096340873412196</v>
       </c>
       <c r="J5" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K5" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08172885227818505</v>
+        <v>0.07677539684918033</v>
       </c>
       <c r="M5" t="n">
-        <v>6.377881123115862</v>
+        <v>6.389276189361811</v>
       </c>
       <c r="N5" t="n">
-        <v>66.26479795967556</v>
+        <v>66.45896114752848</v>
       </c>
       <c r="O5" t="n">
-        <v>8.140319278730752</v>
+        <v>8.15223657332934</v>
       </c>
       <c r="P5" t="n">
-        <v>352.0714577959058</v>
+        <v>351.9534083818702</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36707,28 +36915,28 @@
         <v>0.1118</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3052254154868813</v>
+        <v>-0.29613600199682</v>
       </c>
       <c r="J6" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K6" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06074905501945715</v>
+        <v>0.05784026414071608</v>
       </c>
       <c r="M6" t="n">
-        <v>7.430654390370996</v>
+        <v>7.425663118979016</v>
       </c>
       <c r="N6" t="n">
-        <v>82.45820500806218</v>
+        <v>82.34692904554714</v>
       </c>
       <c r="O6" t="n">
-        <v>9.080650032242305</v>
+        <v>9.074520871404019</v>
       </c>
       <c r="P6" t="n">
-        <v>351.9909172679114</v>
+        <v>351.8962912191674</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36785,28 +36993,28 @@
         <v>0.1316</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3120544269181821</v>
+        <v>-0.3046750751558781</v>
       </c>
       <c r="J7" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K7" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06811157290154501</v>
+        <v>0.06572078559479033</v>
       </c>
       <c r="M7" t="n">
-        <v>7.044784844956118</v>
+        <v>7.036764051832479</v>
       </c>
       <c r="N7" t="n">
-        <v>76.27005863663845</v>
+        <v>76.07089254556716</v>
       </c>
       <c r="O7" t="n">
-        <v>8.733273076953363</v>
+        <v>8.721862905685182</v>
       </c>
       <c r="P7" t="n">
-        <v>355.5533834000174</v>
+        <v>355.4765555954983</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36863,28 +37071,28 @@
         <v>0.1775</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3079419640809525</v>
+        <v>-0.3034685721284955</v>
       </c>
       <c r="J8" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K8" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06875920104304112</v>
+        <v>0.06759801208324223</v>
       </c>
       <c r="M8" t="n">
-        <v>6.847034857052019</v>
+        <v>6.829059099932916</v>
       </c>
       <c r="N8" t="n">
-        <v>73.52233634638212</v>
+        <v>73.22635658549801</v>
       </c>
       <c r="O8" t="n">
-        <v>8.574516682961328</v>
+        <v>8.55724000981029</v>
       </c>
       <c r="P8" t="n">
-        <v>357.7955781259735</v>
+        <v>357.7489766426287</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36941,28 +37149,28 @@
         <v>0.1223</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3559233469070311</v>
+        <v>-0.3484652929477097</v>
       </c>
       <c r="J9" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K9" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09577403361872505</v>
+        <v>0.09289148749238985</v>
       </c>
       <c r="M9" t="n">
-        <v>6.84622893782949</v>
+        <v>6.841210313781625</v>
       </c>
       <c r="N9" t="n">
-        <v>68.46876975009215</v>
+        <v>68.35544269737922</v>
       </c>
       <c r="O9" t="n">
-        <v>8.274585775136551</v>
+        <v>8.267735040346855</v>
       </c>
       <c r="P9" t="n">
-        <v>354.0750202973514</v>
+        <v>353.9973513426132</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37019,28 +37227,28 @@
         <v>0.111</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5091832949666082</v>
+        <v>-0.5009496383284949</v>
       </c>
       <c r="J10" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K10" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2474348035889355</v>
+        <v>0.2423908168434511</v>
       </c>
       <c r="M10" t="n">
-        <v>5.36268567074591</v>
+        <v>5.371720688139789</v>
       </c>
       <c r="N10" t="n">
-        <v>45.14212645615261</v>
+        <v>45.21556062951386</v>
       </c>
       <c r="O10" t="n">
-        <v>6.718789061739668</v>
+        <v>6.724251678031829</v>
       </c>
       <c r="P10" t="n">
-        <v>355.3162880574699</v>
+        <v>355.2305470961877</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37097,28 +37305,28 @@
         <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5587590825212385</v>
+        <v>-0.5510667895549685</v>
       </c>
       <c r="J11" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="K11" t="n">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3475230868987637</v>
+        <v>0.3423562910298162</v>
       </c>
       <c r="M11" t="n">
-        <v>4.683776986012949</v>
+        <v>4.697483138172078</v>
       </c>
       <c r="N11" t="n">
-        <v>33.5568398131566</v>
+        <v>33.62726543894984</v>
       </c>
       <c r="O11" t="n">
-        <v>5.792826582347913</v>
+        <v>5.798902089098404</v>
       </c>
       <c r="P11" t="n">
-        <v>356.9879851968049</v>
+        <v>356.907902295753</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37156,7 +37364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L681"/>
+  <dimension ref="A1:L685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79381,6 +79589,254 @@
         </is>
       </c>
     </row>
+    <row r="682">
+      <c r="A682" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:19:29+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>-43.46592474939944,169.75887315001458</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>-43.46543000036578,169.75946222689436</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>-43.46490350939171,169.7599914236689</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>-43.46433121846247,169.76043061399375</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>-43.46378904978086,169.7609277902512</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>-43.46323502330082,169.76139884034882</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>-43.462689066413915,169.76186837810988</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>-43.462087363943525,169.7621985424324</t>
+        </is>
+      </c>
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>-43.461477177425074,169.76251253869358</t>
+        </is>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>-43.460848387982935,169.762754184731</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:25:37+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>-43.46591468065077,169.7588541845173</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>-43.4654241181385,169.75945114709396</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>-43.46489694432961,169.75997888781126</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>-43.46432592504351,169.7604201716922</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>-43.463784788058184,169.76091922198927</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>-43.46322825755751,169.76138454848416</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>-43.462683919168626,169.76185423546715</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>-43.46208075030969,169.76217477394923</t>
+        </is>
+      </c>
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>-43.46147105173469,169.76248891821427</t>
+        </is>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>-43.46084661996672,169.762747052273</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-22 22:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>-43.4659190791045,169.75886246944427</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>-43.46542501902022,169.75945284400018</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>-43.46487961255942,169.75994579316026</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>-43.46432016909178,169.7604088169586</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>-43.46378199764418,169.76091361181844</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>-43.46322561009227,169.7613789560163</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>-43.46266457677093,169.76180109008962</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>-43.46207278825872,169.76214615947183</t>
+        </is>
+      </c>
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>-43.461464503577645,169.76246366874196</t>
+        </is>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>-43.46084366361078,169.76273512586877</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:19:18+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>-43.4659190791045,169.75886246944427</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>-43.46542501902022,169.75945284400018</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>-43.46487593612216,169.75993877308525</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>-43.464315903519726,169.7604004022914</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>-43.46378199764418,169.76091361181844</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>-43.46322561009227,169.7613789560163</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>-43.46266457677093,169.76180109008962</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>-43.46206540409235,169.7621196218587</t>
+        </is>
+      </c>
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>-43.46145747260115,169.7624365575638</t>
+        </is>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>-43.46084467804677,169.76273921826225</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0436/nzd0436.xlsx
+++ b/data/nzd0436/nzd0436.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L685"/>
+  <dimension ref="A1:L688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29218,6 +29218,132 @@
       <c r="L685" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:19:15+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>356.98</v>
+      </c>
+      <c r="C686" t="n">
+        <v>348.55</v>
+      </c>
+      <c r="D686" t="n">
+        <v>352.89</v>
+      </c>
+      <c r="E686" t="n">
+        <v>355.8</v>
+      </c>
+      <c r="F686" t="n">
+        <v>354.66</v>
+      </c>
+      <c r="G686" t="n">
+        <v>355.78</v>
+      </c>
+      <c r="H686" t="n">
+        <v>359</v>
+      </c>
+      <c r="I686" t="n">
+        <v>356.66</v>
+      </c>
+      <c r="J686" t="n">
+        <v>354.04</v>
+      </c>
+      <c r="K686" t="n">
+        <v>350.2</v>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-15 22:25:30+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>359.58</v>
+      </c>
+      <c r="C687" t="n">
+        <v>348.85</v>
+      </c>
+      <c r="D687" t="n">
+        <v>352.72</v>
+      </c>
+      <c r="E687" t="n">
+        <v>356.04</v>
+      </c>
+      <c r="F687" t="n">
+        <v>355.2</v>
+      </c>
+      <c r="G687" t="n">
+        <v>358.67</v>
+      </c>
+      <c r="H687" t="n">
+        <v>362.21</v>
+      </c>
+      <c r="I687" t="n">
+        <v>357.08</v>
+      </c>
+      <c r="J687" t="n">
+        <v>354.69</v>
+      </c>
+      <c r="K687" t="n">
+        <v>349.96</v>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>360.31</v>
+      </c>
+      <c r="C688" t="n">
+        <v>349.37</v>
+      </c>
+      <c r="D688" t="n">
+        <v>352.56</v>
+      </c>
+      <c r="E688" t="n">
+        <v>356.13</v>
+      </c>
+      <c r="F688" t="n">
+        <v>355.86</v>
+      </c>
+      <c r="G688" t="n">
+        <v>359.36</v>
+      </c>
+      <c r="H688" t="n">
+        <v>361.95</v>
+      </c>
+      <c r="I688" t="n">
+        <v>357.01</v>
+      </c>
+      <c r="J688" t="n">
+        <v>355.07</v>
+      </c>
+      <c r="K688" t="n">
+        <v>348.78</v>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29232,7 +29358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B720"/>
+  <dimension ref="A1:B723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36435,6 +36561,36 @@
       </c>
       <c r="B720" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B721" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>2026-06-15 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B722" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B723" t="n">
+        <v>0.5600000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -36603,28 +36759,28 @@
         <v>0.09130000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5724045200626597</v>
+        <v>-0.5700769614916156</v>
       </c>
       <c r="J2" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K2" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L2" t="n">
-        <v>0.273526280119009</v>
+        <v>0.2736384129507921</v>
       </c>
       <c r="M2" t="n">
-        <v>5.593870189135133</v>
+        <v>5.579816685858884</v>
       </c>
       <c r="N2" t="n">
-        <v>50.16463718059923</v>
+        <v>49.98725656242565</v>
       </c>
       <c r="O2" t="n">
-        <v>7.082699851087806</v>
+        <v>7.070166657330338</v>
       </c>
       <c r="P2" t="n">
-        <v>371.5534860175762</v>
+        <v>371.5291651962772</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36681,28 +36837,28 @@
         <v>0.1156</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.53008573159374</v>
+        <v>-0.5248476626118423</v>
       </c>
       <c r="J3" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K3" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2030464988578015</v>
+        <v>0.2009611813276294</v>
       </c>
       <c r="M3" t="n">
-        <v>6.492636965242941</v>
+        <v>6.492741571741124</v>
       </c>
       <c r="N3" t="n">
-        <v>63.57705747345776</v>
+        <v>63.46565319269973</v>
       </c>
       <c r="O3" t="n">
-        <v>7.973522275221771</v>
+        <v>7.96653332339103</v>
       </c>
       <c r="P3" t="n">
-        <v>356.9381301355536</v>
+        <v>356.8834082845514</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36759,28 +36915,28 @@
         <v>0.1199</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4029292295784565</v>
+        <v>-0.3934578924166787</v>
       </c>
       <c r="J4" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K4" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1395040811515191</v>
+        <v>0.1339094328552858</v>
       </c>
       <c r="M4" t="n">
-        <v>5.98794151875324</v>
+        <v>6.003880245095612</v>
       </c>
       <c r="N4" t="n">
-        <v>57.72848577988985</v>
+        <v>58.0183236340639</v>
       </c>
       <c r="O4" t="n">
-        <v>7.597926413166283</v>
+        <v>7.616976016377096</v>
       </c>
       <c r="P4" t="n">
-        <v>352.311912442501</v>
+        <v>352.2129683056093</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36837,28 +36993,28 @@
         <v>0.0997</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3096340873412196</v>
+        <v>-0.2992117032407156</v>
       </c>
       <c r="J5" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K5" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07677539684918033</v>
+        <v>0.07203855674619564</v>
       </c>
       <c r="M5" t="n">
-        <v>6.389276189361811</v>
+        <v>6.40731219763666</v>
       </c>
       <c r="N5" t="n">
-        <v>66.45896114752848</v>
+        <v>66.82494296140668</v>
       </c>
       <c r="O5" t="n">
-        <v>8.15223657332934</v>
+        <v>8.17465246731668</v>
       </c>
       <c r="P5" t="n">
-        <v>351.9534083818702</v>
+        <v>351.8445279268542</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36915,28 +37071,28 @@
         <v>0.1118</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.29613600199682</v>
+        <v>-0.2866055124856304</v>
       </c>
       <c r="J6" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K6" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05784026414071608</v>
+        <v>0.05452396481184341</v>
       </c>
       <c r="M6" t="n">
-        <v>7.425663118979016</v>
+        <v>7.433054107801258</v>
       </c>
       <c r="N6" t="n">
-        <v>82.34692904554714</v>
+        <v>82.53700215426674</v>
       </c>
       <c r="O6" t="n">
-        <v>9.074520871404019</v>
+        <v>9.084987735504475</v>
       </c>
       <c r="P6" t="n">
-        <v>351.8962912191674</v>
+        <v>351.7967269944252</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36993,28 +37149,28 @@
         <v>0.1316</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3046750751558781</v>
+        <v>-0.2956973041328465</v>
       </c>
       <c r="J7" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K7" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06572078559479033</v>
+        <v>0.06231709538743568</v>
       </c>
       <c r="M7" t="n">
-        <v>7.036764051832479</v>
+        <v>7.045975204256022</v>
       </c>
       <c r="N7" t="n">
-        <v>76.07089254556716</v>
+        <v>76.23598950313531</v>
       </c>
       <c r="O7" t="n">
-        <v>8.721862905685182</v>
+        <v>8.731322322714659</v>
       </c>
       <c r="P7" t="n">
-        <v>355.4765555954983</v>
+        <v>355.3827612672646</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37071,28 +37227,28 @@
         <v>0.1775</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3034685721284955</v>
+        <v>-0.2938065241193754</v>
       </c>
       <c r="J8" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K8" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06759801208324223</v>
+        <v>0.06373406819518801</v>
       </c>
       <c r="M8" t="n">
-        <v>6.829059099932916</v>
+        <v>6.846606625018135</v>
       </c>
       <c r="N8" t="n">
-        <v>73.22635658549801</v>
+        <v>73.4796309622209</v>
       </c>
       <c r="O8" t="n">
-        <v>8.55724000981029</v>
+        <v>8.572026071018502</v>
       </c>
       <c r="P8" t="n">
-        <v>357.7489766426287</v>
+        <v>357.6480343064176</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37149,28 +37305,28 @@
         <v>0.1223</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3484652929477097</v>
+        <v>-0.3381099180978995</v>
       </c>
       <c r="J9" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K9" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09289148749238985</v>
+        <v>0.08793672230441529</v>
       </c>
       <c r="M9" t="n">
-        <v>6.841210313781625</v>
+        <v>6.860428409988821</v>
       </c>
       <c r="N9" t="n">
-        <v>68.35544269737922</v>
+        <v>68.70479260190692</v>
       </c>
       <c r="O9" t="n">
-        <v>8.267735040346855</v>
+        <v>8.288835418917841</v>
       </c>
       <c r="P9" t="n">
-        <v>353.9973513426132</v>
+        <v>353.8891707659232</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37227,28 +37383,28 @@
         <v>0.111</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5009496383284949</v>
+        <v>-0.4901351069384349</v>
       </c>
       <c r="J10" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K10" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2423908168434511</v>
+        <v>0.2333832908635221</v>
       </c>
       <c r="M10" t="n">
-        <v>5.371720688139789</v>
+        <v>5.402385209313714</v>
       </c>
       <c r="N10" t="n">
-        <v>45.21556062951386</v>
+        <v>45.7253100488532</v>
       </c>
       <c r="O10" t="n">
-        <v>6.724251678031829</v>
+        <v>6.762049249218258</v>
       </c>
       <c r="P10" t="n">
-        <v>355.2305470961877</v>
+        <v>355.1175689194116</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37305,28 +37461,28 @@
         <v>0.125</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5510667895549685</v>
+        <v>-0.5447174585218069</v>
       </c>
       <c r="J11" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="K11" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3423562910298162</v>
+        <v>0.3376604353719832</v>
       </c>
       <c r="M11" t="n">
-        <v>4.697483138172078</v>
+        <v>4.71082080421463</v>
       </c>
       <c r="N11" t="n">
-        <v>33.62726543894984</v>
+        <v>33.72559556663828</v>
       </c>
       <c r="O11" t="n">
-        <v>5.798902089098404</v>
+        <v>5.807374240277466</v>
       </c>
       <c r="P11" t="n">
-        <v>356.907902295753</v>
+        <v>356.8415741470631</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37364,7 +37520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L685"/>
+  <dimension ref="A1:L688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79837,6 +79993,192 @@
         </is>
       </c>
     </row>
+    <row r="686">
+      <c r="A686" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:19:15+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>-43.465917966242756,169.75886037325782</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>-43.46542607888103,169.7594548403605</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>-43.46486685006833,169.759921423475</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>-43.464311432377286,169.76039158209932</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>-43.463770176432945,169.76088984510056</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>-43.46321850115656,169.76136393920686</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>-43.462653437791026,169.76177048455548</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>-43.46205882254772,169.76209596877447</t>
+        </is>
+      </c>
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>-43.46145222199661,169.76241631145223</t>
+        </is>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>-43.46084186660952,169.76272787648642</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-15 22:25:30+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>-43.46590418795161,169.7588344204796</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>-43.46542448908979,169.75945184582002</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-43.46486774291766,169.75992312834975</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-43.46431019895857,169.76038914894312</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>-43.46376743675241,169.76088433693553</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>-43.46320433230669,169.7613340091629</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>-43.462640529432605,169.761735017507</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>-43.46205747413311,169.7620911227774</t>
+        </is>
+      </c>
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>-43.46145026056296,169.76240874825058</t>
+        </is>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>-43.46084256222295,169.7627306826989</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:11+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>-43.46590031943039,169.75882713374014</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>-43.465421733451464,169.7594466552836</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-43.464868583246414,169.7599247329378</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-43.46430973642655,169.76038823650956</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>-43.463764088253654,169.7608776047345</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>-43.4632009494314,169.76132686323754</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>-43.46264157496983,169.76173789022684</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>-43.4620576988689,169.76209193044357</t>
+        </is>
+      </c>
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>-43.46144911387848,169.76240432668678</t>
+        </is>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>-43.46084598232143,169.7627444799112</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
